--- a/data/availability/projects/la-vista-developments/la-vista-bay-east.xlsx
+++ b/data/availability/projects/la-vista-developments/la-vista-bay-east.xlsx
@@ -457,16 +457,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Template for La Vista Bay East</t>
+          <t>Live inventory for la-vista-bay-east</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,6 +543,56 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>payment_plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>la-vista-bay-east</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>150</v>
+      </c>
+      <c r="F2" t="n">
+        <v>150</v>
+      </c>
+      <c r="G2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H2" t="n">
+        <v>24</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>5% DP + 7 years</t>
         </is>
       </c>
     </row>
@@ -557,7 +607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -624,6 +674,124 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>la-vista-bay-east</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>LVBE-CH101</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>150</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>5% DP + 7 years</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>la-vista-bay-east</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>LVBE-CHG01</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>150</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Garden: 60 sqm</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>24000000</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>5% DP + 7 years</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Available</t>
         </is>
       </c>
     </row>

--- a/data/availability/projects/la-vista-developments/la-vista-bay-east.xlsx
+++ b/data/availability/projects/la-vista-developments/la-vista-bay-east.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for la-vista-bay-east</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -992,7 +1002,6 @@
       <c r="G5" t="n">
         <v>150</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>

--- a/data/availability/projects/la-vista-developments/la-vista-bay-east.xlsx
+++ b/data/availability/projects/la-vista-developments/la-vista-bay-east.xlsx
@@ -697,7 +697,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>April 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>April 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>April 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
